--- a/reports/pdf_change_20260730.xlsx
+++ b/reports/pdf_change_20260730.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,706억   ·   현금 146억(4.3%)      당일 2026-07-30  vs  전영업일 2026-07-29      매수 4종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,438억   ·   현금 147억(4.3%)      당일 2026-07-30  vs  전영업일 2026-07-29      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>318111000</v>
+        <v>320679000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-32</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1595113600</v>
+        <v>-1607990400</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>151920300</v>
+        <v>153146700</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-18</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-445950000</v>
+        <v>-449550000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>271930400</v>
+        <v>274125600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-13</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1212290300</v>
+        <v>-1222076700</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>135122850</v>
+        <v>136213650</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,347억   ·   현금 13억(0.4%)      당일 2026-07-30  vs  전영업일 2026-07-29      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,104억   ·   현금 13억(0.4%)      당일 2026-07-30  vs  전영업일 2026-07-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -845,241 +845,257 @@
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="20" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
-      <c r="K14" s="20" t="n"/>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="20" t="n"/>
-      <c r="I16" s="20" t="n"/>
-      <c r="J16" s="20" t="n"/>
-      <c r="K16" s="20" t="n"/>
-    </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 239억   ·   현금 7억(3.0%)      당일 2026-07-30  vs  전영업일 2026-07-29      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,929억   ·   현금 34억(1.8%)      당일 2026-07-30  vs  전영업일 2026-07-29      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 454억   ·   현금 10억(2.3%)      당일 2026-07-30  vs  전영업일 2026-07-29      매수 0종목  /  매도 2종목</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,829억   ·   현금 27억(1.5%)      당일 2026-07-30  vs  전영업일 2026-07-29      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 218억   ·   현금 7억(3.2%)      당일 2026-07-30  vs  전영업일 2026-07-29      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 433억   ·   현금 10억(2.3%)      당일 2026-07-30  vs  전영업일 2026-07-29      매수 0종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="G24" s="14" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="17" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="H24" s="15" t="n">
+      <c r="H26" s="15" t="n">
         <v>-21</v>
       </c>
-      <c r="I24" s="15" t="n">
-        <v>-412020000</v>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="I26" s="15" t="n">
+        <v>-415800000</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>9.45%→9.39%</t>
         </is>
       </c>
-      <c r="K24" s="13" t="inlineStr">
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>218→197</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="17" t="n"/>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="G25" s="14" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="17" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H27" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I25" s="15" t="n">
-        <v>-153962500</v>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="I27" s="15" t="n">
+        <v>-155375000</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>9.86%→9.80%</t>
         </is>
       </c>
-      <c r="K25" s="13" t="inlineStr">
+      <c r="K27" s="13" t="inlineStr">
         <is>
           <t>136→131</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="20" t="n"/>
-      <c r="H27" s="20" t="n"/>
-      <c r="I27" s="20" t="n"/>
-      <c r="J27" s="20" t="n"/>
-      <c r="K27" s="20" t="n"/>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="20" t="n"/>
+      <c r="G29" s="20" t="n"/>
+      <c r="H29" s="20" t="n"/>
+      <c r="I29" s="20" t="n"/>
+      <c r="J29" s="20" t="n"/>
+      <c r="K29" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A20:K20"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="A29:K29"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="G22:K22"/>
     <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A22:E22"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A17:K17"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
